--- a/output/身体拘束適正化委員会_研修実施報告書_R8.7.25.xlsx
+++ b/output/身体拘束適正化委員会_研修実施報告書_R8.7.25.xlsx
@@ -540,10 +540,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:D28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -853,6 +853,8 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>